--- a/Employee_Reports_wi52/Naser Qasim Mohammad Alhaj Ahmed Q0534.xlsx
+++ b/Employee_Reports_wi52/Naser Qasim Mohammad Alhaj Ahmed Q0534.xlsx
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-388</v>
+        <v>-396</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -606,11 +606,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-37</v>
+        <v>-45</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -643,11 +643,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
